--- a/data/trans_camb/P1426-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1426-Edad-trans_camb.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,3</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,13</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; -0,14</t>
+          <t>-2,09; -0,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,51</t>
+          <t>-1,69; 0,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,84</t>
+          <t>-1,04; 0,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,94</t>
+          <t>-0,52; 1,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,18</t>
+          <t>-1,17; 0,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,01</t>
+          <t>-0,62; 0,92</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-57,23%</t>
+          <t>-63,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>110,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 577,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,57; 1619,97</t>
+          <t>-74,27; 1004,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-92,53; 174,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,22; 361,31</t>
+          <t>-65,11; 415,53</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,0</t>
+          <t>-1,47; -0,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,38</t>
+          <t>-0,27; 2,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,72</t>
+          <t>-1,06; 0,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,1</t>
+          <t>-1,43; 0,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,15</t>
+          <t>-0,97; 0,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,98</t>
+          <t>-0,43; 1,04</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>123,42%</t>
+          <t>117,85%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-63,83%</t>
+          <t>-52,62%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,07; 758,49</t>
+          <t>-39,55; 605,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-94,51; 423,5</t>
+          <t>-100,0; 500,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 234,45</t>
+          <t>-100,0; 246,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-89,38; 68,59</t>
+          <t>-86,32; 73,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 259,16</t>
+          <t>-47,59; 274,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,81</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,63</t>
+          <t>-0,65; 1,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,43</t>
+          <t>1,2; 4,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,69</t>
+          <t>-1,49; 0,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,15</t>
+          <t>-0,05; 2,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,8</t>
+          <t>-0,73; 0,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,3</t>
+          <t>0,81; 2,76</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>252,96%</t>
+          <t>369,02%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102,89%</t>
+          <t>112,92%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>164,96%</t>
+          <t>213,78%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 669,47</t>
+          <t>-66,97; 585,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1186,95</t>
+          <t>63,76; 1765,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-88,09; 208,45</t>
+          <t>-89,23; 184,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 512,68</t>
+          <t>-8,68; 597,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,49; 186,33</t>
+          <t>-60,44; 174,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,81; 487,52</t>
+          <t>53,09; 575,97</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>2,77</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,29</t>
+          <t>-2,09; 2,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,6</t>
+          <t>0,81; 5,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,73</t>
+          <t>-0,33; 3,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,02</t>
+          <t>0,83; 4,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,25</t>
+          <t>-0,79; 2,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,41</t>
+          <t>1,31; 4,05</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>132,75%</t>
+          <t>119,29%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>170,06%</t>
+          <t>179,19%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>148,33%</t>
+          <t>142,14%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 157,07</t>
+          <t>-64,23; 178,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14,48; 346,11</t>
+          <t>15,5; 404,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 561,98</t>
+          <t>-28,51; 522,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15,34; 637,65</t>
+          <t>16,41; 593,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 196,31</t>
+          <t>-31,11; 159,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,8; 334,3</t>
+          <t>43,2; 320,94</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>4,03</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,94</t>
+          <t>-7,77; -1,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,35</t>
+          <t>-1,08; 6,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,65</t>
+          <t>1,9; 7,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,68</t>
+          <t>2,57; 7,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,61</t>
+          <t>-1,48; 2,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,74</t>
+          <t>1,77; 5,96</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133,03%</t>
+          <t>252,49%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>110,27%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-89,28; -15,13</t>
+          <t>-90,51; -21,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 181,85</t>
+          <t>-15,67; 169,53</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>56,59; 825,4</t>
+          <t>47,35; 748,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 445,18</t>
+          <t>61,84; 710,95</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 90,87</t>
+          <t>-30,56; 104,93</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 165,4</t>
+          <t>32,26; 231,05</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>16,19</t>
+          <t>15,83</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>10,51</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,91</t>
+          <t>12,59</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 8,35</t>
+          <t>0,37; 8,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11,46; 20,51</t>
+          <t>11,43; 20,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -0,38</t>
+          <t>-8,36; -0,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,18; 14,51</t>
+          <t>6,37; 14,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,97</t>
+          <t>-3,72; 2,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,94</t>
+          <t>9,0; 15,45</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>381,51%</t>
+          <t>372,99%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110,52%</t>
+          <t>107,54%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>169,62%</t>
+          <t>165,41%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0,5; 352,33</t>
+          <t>3,98; 359,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>160,37; 927,98</t>
+          <t>167,75; 905,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-68,03; 2,46</t>
+          <t>-70,01; -3,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47,03; 192,4</t>
+          <t>51,13; 186,92</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 34,35</t>
+          <t>-40,88; 38,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>94,27; 267,28</t>
+          <t>94,48; 269,7</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,97</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,46</t>
+          <t>-0,72; 0,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,76</t>
+          <t>2,38; 3,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,89</t>
+          <t>-0,54; 0,86</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,3</t>
+          <t>2,11; 3,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,43</t>
+          <t>-0,43; 0,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,41</t>
+          <t>2,4; 3,49</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>189,51%</t>
+          <t>201,88%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>136,81%</t>
+          <t>152,53%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>160,23%</t>
+          <t>174,49%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 36,29</t>
+          <t>-38,84; 44,58</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>97,18; 293,7</t>
+          <t>122,68; 321,49</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 58,11</t>
+          <t>-24,7; 52,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>72,18; 220,99</t>
+          <t>92,83; 231,4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 28,41</t>
+          <t>-22,76; 36,34</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>107,48; 230,77</t>
+          <t>118,05; 238,58</t>
         </is>
       </c>
     </row>
